--- a/FaunalListoR_data.xlsx
+++ b/FaunalListoR_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t xml:space="preserve">id_faunalstudy</t>
   </si>
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Bois Ragot</t>
   </si>
   <si>
-    <t xml:space="preserve">Chevallier 2015 thèse</t>
+    <t xml:space="preserve">Chevallier, A. (2015). Chasse et traitement des mammifères durant le Magdalénien et l'Azilien dans le Sud-Ouest de la France: la place particulière du Cerf (Doctoral dissertation, Paris 1).</t>
   </si>
   <si>
     <t xml:space="preserve">Morpho</t>
@@ -51,13 +51,19 @@
     <t xml:space="preserve">NISP</t>
   </si>
   <si>
-    <t xml:space="preserve">Cuzoul de Gramat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abeurador</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">Moulin du Roc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jones, E. L. (2006). Prey choice, mass collecting, and the wild European rabbit (Oryctolagus cuniculus). Journal of Anthropological Archaeology, 25(3), 275-289.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peyrazet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sandrine Costamagno. La grande faune de Peyrazet : nouvel exemple de l’importance du renne dans les modes de vie des groupes magdaléniens de la zone Pégigord-Quercy. Langlais M. and V. Laroulandie (dir.). La grotte-abri de Peyrazet (Creysse, Lot, France) au Magdalénien. Originalité fonctionnelle d’un habitat des derniers chasseurs de rennes du Quercy, 43, CNRS Éditions, pp.127-139, 2021, Gallia Préhistoire Supplément, 978-2-271-13647-3. ff10.4000/books.editionscnrs.55875ff.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">faunal study combines couches 4 et 5</t>
   </si>
   <si>
     <t xml:space="preserve">taxon_unified</t>
@@ -87,202 +93,112 @@
     <t xml:space="preserve">BR3</t>
   </si>
   <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canis sp.</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
     <t xml:space="preserve">Capreolus capreolus</t>
   </si>
   <si>
-    <t xml:space="preserve">33</t>
-  </si>
-  <si>
     <t xml:space="preserve">Castor fiber</t>
   </si>
   <si>
     <t xml:space="preserve">Cervus elaphus</t>
   </si>
   <si>
-    <t xml:space="preserve">196</t>
-  </si>
-  <si>
     <t xml:space="preserve">Equus ferus</t>
   </si>
   <si>
     <t xml:space="preserve">Equus caballus</t>
   </si>
   <si>
-    <t xml:space="preserve">13</t>
+    <t xml:space="preserve">Felis silvestris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lepus sp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Martes sp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meles meles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oryctolagus cuniculus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rangifer tarandus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rupicapra sp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sus scrofa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vulpes vulpes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR4</t>
   </si>
   <si>
     <t xml:space="preserve">Equus hydruntinus</t>
   </si>
   <si>
-    <t xml:space="preserve">Felis silvestris</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lepus sp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martes sp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meles meles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oryctolagus cuniculus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rangifer tarandus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rupicapra sp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sus scrofa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vulpes vulpes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anoura geoffroyi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mégacéros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HA2.1 / 2.3 - SG5100-5110-5200-5300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ens2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ens3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ens1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ens4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ens5</t>
+    <t xml:space="preserve">Bos/Bison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">couche brune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">couche brune-bigarrée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bigarée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">couche jaune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jaune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bovinés indéterminés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">couches.4.et.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canis lupus</t>
   </si>
   <si>
     <t xml:space="preserve">Capra ibex/pyrenaica</t>
   </si>
   <si>
-    <t xml:space="preserve">Bouquetin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chevreuil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cerf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cheval</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hydrontin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proboscidae</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proboscidiens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chamois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SC-SF c.2a</t>
+    <t xml:space="preserve">Capra ibex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caprinae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caprinés indéterminés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cervidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cervidés indéterminés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lynx spelaea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rupicapra rupicapra</t>
   </si>
 </sst>
 </file>
@@ -651,7 +567,7 @@
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
@@ -669,10 +585,14 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>94</v>
-      </c>
-      <c r="D3"/>
-      <c r="E3"/>
+        <v>11519</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2006</v>
+      </c>
       <c r="F3" t="s">
         <v>10</v>
       </c>
@@ -686,15 +606,17 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>671</v>
+        <v>1994</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4"/>
+        <v>15</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2021</v>
+      </c>
       <c r="F4" t="s">
         <v>10</v>
       </c>
@@ -702,7 +624,7 @@
         <v>11</v>
       </c>
       <c r="H4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -721,22 +643,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -747,22 +669,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" t="n">
         <v>19490</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G2" t="n">
+        <v>18</v>
       </c>
       <c r="H2" t="s">
         <v>11</v>
@@ -773,22 +695,22 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
         <v>19490</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
       </c>
       <c r="H3" t="s">
         <v>11</v>
@@ -808,13 +730,13 @@
         <v>19490</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33</v>
       </c>
       <c r="H4" t="s">
         <v>11</v>
@@ -825,22 +747,22 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="n">
         <v>19490</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G5" t="n">
+        <v>18</v>
       </c>
       <c r="H5" t="s">
         <v>11</v>
@@ -851,22 +773,22 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
         <v>19490</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
+        <v>25</v>
+      </c>
+      <c r="G6" t="n">
+        <v>196</v>
       </c>
       <c r="H6" t="s">
         <v>11</v>
@@ -877,22 +799,22 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" t="n">
         <v>19490</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" t="s">
-        <v>34</v>
+        <v>25</v>
+      </c>
+      <c r="G7" t="n">
+        <v>13</v>
       </c>
       <c r="H7" t="s">
         <v>11</v>
@@ -903,21 +825,23 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
         <v>19490</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8"/>
+        <v>25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
       <c r="H8" t="s">
         <v>11</v>
       </c>
@@ -927,22 +851,22 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D9" t="n">
         <v>19490</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>37</v>
+        <v>25</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
       </c>
       <c r="H9" t="s">
         <v>11</v>
@@ -953,22 +877,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D10" t="n">
         <v>19490</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
       </c>
       <c r="H10" t="s">
         <v>11</v>
@@ -979,22 +903,22 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D11" t="n">
         <v>19490</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" t="s">
-        <v>41</v>
+        <v>25</v>
+      </c>
+      <c r="G11" t="n">
+        <v>8</v>
       </c>
       <c r="H11" t="s">
         <v>11</v>
@@ -1005,22 +929,22 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D12" t="n">
         <v>19490</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" t="s">
-        <v>43</v>
+        <v>25</v>
+      </c>
+      <c r="G12" t="n">
+        <v>107</v>
       </c>
       <c r="H12" t="s">
         <v>11</v>
@@ -1031,22 +955,22 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
         <v>19490</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" t="s">
-        <v>45</v>
+        <v>25</v>
+      </c>
+      <c r="G13" t="n">
+        <v>18</v>
       </c>
       <c r="H13" t="s">
         <v>11</v>
@@ -1057,22 +981,22 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
         <v>19490</v>
       </c>
       <c r="E14" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9</v>
       </c>
       <c r="H14" t="s">
         <v>11</v>
@@ -1083,22 +1007,22 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>19490</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" t="s">
-        <v>48</v>
+        <v>25</v>
+      </c>
+      <c r="G15" t="n">
+        <v>26</v>
       </c>
       <c r="H15" t="s">
         <v>11</v>
@@ -1109,22 +1033,22 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>19490</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
-      </c>
-      <c r="G16" t="s">
-        <v>50</v>
+        <v>25</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9</v>
       </c>
       <c r="H16" t="s">
         <v>11</v>
@@ -1135,22 +1059,22 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="D17" t="n">
-        <v>19490</v>
+        <v>19491</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" t="s">
-        <v>48</v>
+        <v>41</v>
+      </c>
+      <c r="G17" t="n">
+        <v>90</v>
       </c>
       <c r="H17" t="s">
         <v>11</v>
@@ -1161,22 +1085,22 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>19491</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>52</v>
-      </c>
-      <c r="G18" t="s">
-        <v>53</v>
+        <v>41</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
       </c>
       <c r="H18" t="s">
         <v>11</v>
@@ -1187,22 +1111,22 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>19491</v>
       </c>
       <c r="E19" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
-      </c>
-      <c r="G19" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="G19" t="n">
+        <v>55</v>
       </c>
       <c r="H19" t="s">
         <v>11</v>
@@ -1213,22 +1137,22 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>19491</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F20" t="s">
-        <v>52</v>
-      </c>
-      <c r="G20" t="s">
-        <v>54</v>
+        <v>41</v>
+      </c>
+      <c r="G20" t="n">
+        <v>37</v>
       </c>
       <c r="H20" t="s">
         <v>11</v>
@@ -1248,13 +1172,13 @@
         <v>19491</v>
       </c>
       <c r="E21" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F21" t="s">
-        <v>52</v>
-      </c>
-      <c r="G21" t="s">
-        <v>55</v>
+        <v>41</v>
+      </c>
+      <c r="G21" t="n">
+        <v>664</v>
       </c>
       <c r="H21" t="s">
         <v>11</v>
@@ -1268,19 +1192,19 @@
         <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D22" t="n">
         <v>19491</v>
       </c>
       <c r="E22" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>52</v>
-      </c>
-      <c r="G22" t="s">
-        <v>56</v>
+        <v>41</v>
+      </c>
+      <c r="G22" t="n">
+        <v>57</v>
       </c>
       <c r="H22" t="s">
         <v>11</v>
@@ -1291,22 +1215,22 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D23" t="n">
         <v>19491</v>
       </c>
       <c r="E23" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>52</v>
-      </c>
-      <c r="G23" t="s">
-        <v>57</v>
+        <v>41</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
       </c>
       <c r="H23" t="s">
         <v>11</v>
@@ -1317,22 +1241,22 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C24" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D24" t="n">
         <v>19491</v>
       </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>52</v>
-      </c>
-      <c r="G24" t="s">
-        <v>26</v>
+        <v>41</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4</v>
       </c>
       <c r="H24" t="s">
         <v>11</v>
@@ -1343,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="D25" t="n">
         <v>19491</v>
       </c>
       <c r="E25" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
-      </c>
-      <c r="G25" t="s">
-        <v>39</v>
+        <v>41</v>
+      </c>
+      <c r="G25" t="n">
+        <v>50</v>
       </c>
       <c r="H25" t="s">
         <v>11</v>
@@ -1369,22 +1293,22 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D26" t="n">
         <v>19491</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
-      </c>
-      <c r="G26" t="s">
-        <v>58</v>
+        <v>41</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
       </c>
       <c r="H26" t="s">
         <v>11</v>
@@ -1395,22 +1319,22 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D27" t="n">
         <v>19491</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F27" t="s">
-        <v>52</v>
-      </c>
-      <c r="G27" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="G27" t="n">
+        <v>47</v>
       </c>
       <c r="H27" t="s">
         <v>11</v>
@@ -1421,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C28" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D28" t="n">
         <v>19491</v>
       </c>
       <c r="E28" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F28" t="s">
-        <v>52</v>
-      </c>
-      <c r="G28" t="s">
-        <v>59</v>
+        <v>41</v>
+      </c>
+      <c r="G28" t="n">
+        <v>171</v>
       </c>
       <c r="H28" t="s">
         <v>11</v>
@@ -1447,22 +1371,22 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="D29" t="n">
         <v>19491</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>52</v>
-      </c>
-      <c r="G29" t="s">
-        <v>60</v>
+        <v>41</v>
+      </c>
+      <c r="G29" t="n">
+        <v>72</v>
       </c>
       <c r="H29" t="s">
         <v>11</v>
@@ -1473,22 +1397,22 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C30" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D30" t="n">
         <v>19491</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
-      </c>
-      <c r="G30" t="s">
-        <v>61</v>
+        <v>41</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
       </c>
       <c r="H30" t="s">
         <v>11</v>
@@ -1499,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D31" t="n">
         <v>19491</v>
       </c>
       <c r="E31" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
-      </c>
-      <c r="G31" t="s">
-        <v>41</v>
+        <v>41</v>
+      </c>
+      <c r="G31" t="n">
+        <v>211</v>
       </c>
       <c r="H31" t="s">
         <v>11</v>
@@ -1525,22 +1449,22 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="D32" t="n">
         <v>19491</v>
       </c>
       <c r="E32" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
-      </c>
-      <c r="G32" t="s">
-        <v>62</v>
+        <v>41</v>
+      </c>
+      <c r="G32" t="n">
+        <v>38</v>
       </c>
       <c r="H32" t="s">
         <v>11</v>
@@ -1548,25 +1472,25 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D33" t="n">
-        <v>19491</v>
+        <v>22405</v>
       </c>
       <c r="E33" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F33" t="s">
-        <v>52</v>
-      </c>
-      <c r="G33" t="s">
-        <v>63</v>
+        <v>45</v>
+      </c>
+      <c r="G33" t="n">
+        <v>3</v>
       </c>
       <c r="H33" t="s">
         <v>11</v>
@@ -1577,22 +1501,22 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="D34" t="n">
-        <v>190</v>
+        <v>22405</v>
       </c>
       <c r="E34" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F34" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34" t="s">
-        <v>26</v>
+        <v>45</v>
+      </c>
+      <c r="G34" t="n">
+        <v>17</v>
       </c>
       <c r="H34" t="s">
         <v>11</v>
@@ -1603,22 +1527,22 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="D35" t="n">
-        <v>190</v>
+        <v>22405</v>
       </c>
       <c r="E35" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F35" t="s">
-        <v>68</v>
-      </c>
-      <c r="G35" t="s">
-        <v>26</v>
+        <v>45</v>
+      </c>
+      <c r="G35" t="n">
+        <v>34</v>
       </c>
       <c r="H35" t="s">
         <v>11</v>
@@ -1629,22 +1553,22 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D36" t="n">
-        <v>190</v>
+        <v>22405</v>
       </c>
       <c r="E36" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F36" t="s">
-        <v>69</v>
-      </c>
-      <c r="G36" t="s">
-        <v>70</v>
+        <v>45</v>
+      </c>
+      <c r="G36" t="n">
+        <v>11</v>
       </c>
       <c r="H36" t="s">
         <v>11</v>
@@ -1655,22 +1579,22 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D37" t="n">
-        <v>190</v>
+        <v>22405</v>
       </c>
       <c r="E37" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F37" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37" t="s">
-        <v>71</v>
+        <v>45</v>
+      </c>
+      <c r="G37" t="n">
+        <v>5</v>
       </c>
       <c r="H37" t="s">
         <v>11</v>
@@ -1681,22 +1605,22 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D38" t="n">
-        <v>190</v>
+        <v>22405</v>
       </c>
       <c r="E38" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F38" t="s">
-        <v>68</v>
-      </c>
-      <c r="G38" t="s">
-        <v>50</v>
+        <v>45</v>
+      </c>
+      <c r="G38" t="n">
+        <v>6596</v>
       </c>
       <c r="H38" t="s">
         <v>11</v>
@@ -1707,25 +1631,25 @@
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D39" t="n">
-        <v>190</v>
+        <v>22405</v>
       </c>
       <c r="E39" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F39" t="s">
-        <v>72</v>
-      </c>
-      <c r="G39" t="s">
-        <v>73</v>
+        <v>45</v>
+      </c>
+      <c r="G39" t="n">
+        <v>115</v>
       </c>
       <c r="H39" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -1733,22 +1657,22 @@
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D40" t="n">
-        <v>190</v>
+        <v>22405</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="F40" t="s">
-        <v>75</v>
-      </c>
-      <c r="G40" t="s">
-        <v>24</v>
+        <v>45</v>
+      </c>
+      <c r="G40" t="n">
+        <v>23</v>
       </c>
       <c r="H40" t="s">
         <v>11</v>
@@ -1759,22 +1683,22 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
       <c r="C41" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="D41" t="n">
-        <v>190</v>
+        <v>22406</v>
       </c>
       <c r="E41" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="F41" t="s">
-        <v>69</v>
-      </c>
-      <c r="G41" t="s">
-        <v>37</v>
+        <v>47</v>
+      </c>
+      <c r="G41" t="n">
+        <v>7</v>
       </c>
       <c r="H41" t="s">
         <v>11</v>
@@ -1785,22 +1709,22 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>29</v>
       </c>
       <c r="C42" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="D42" t="n">
-        <v>190</v>
+        <v>22406</v>
       </c>
       <c r="E42" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="F42" t="s">
-        <v>67</v>
-      </c>
-      <c r="G42" t="s">
-        <v>39</v>
+        <v>47</v>
+      </c>
+      <c r="G42" t="n">
+        <v>5</v>
       </c>
       <c r="H42" t="s">
         <v>11</v>
@@ -1811,22 +1735,22 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="D43" t="n">
-        <v>190</v>
+        <v>22406</v>
       </c>
       <c r="E43" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="F43" t="s">
-        <v>68</v>
-      </c>
-      <c r="G43" t="s">
-        <v>41</v>
+        <v>47</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>11</v>
@@ -1837,22 +1761,22 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
       <c r="D44" t="n">
-        <v>190</v>
+        <v>22406</v>
       </c>
       <c r="E44" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="F44" t="s">
-        <v>68</v>
-      </c>
-      <c r="G44" t="s">
-        <v>26</v>
+        <v>47</v>
+      </c>
+      <c r="G44" t="n">
+        <v>230</v>
       </c>
       <c r="H44" t="s">
         <v>11</v>
@@ -1863,25 +1787,25 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C45" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="D45" t="n">
-        <v>190</v>
+        <v>22406</v>
       </c>
       <c r="E45" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="F45" t="s">
-        <v>72</v>
-      </c>
-      <c r="G45" t="s">
-        <v>26</v>
+        <v>47</v>
+      </c>
+      <c r="G45" t="n">
+        <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46">
@@ -1889,22 +1813,22 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C46" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="D46" t="n">
-        <v>190</v>
+        <v>22407</v>
       </c>
       <c r="E46" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F46" t="s">
-        <v>75</v>
-      </c>
-      <c r="G46" t="s">
-        <v>39</v>
+        <v>49</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3</v>
       </c>
       <c r="H46" t="s">
         <v>11</v>
@@ -1915,22 +1839,22 @@
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C47" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="D47" t="n">
-        <v>190</v>
+        <v>22407</v>
       </c>
       <c r="E47" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F47" t="s">
-        <v>69</v>
-      </c>
-      <c r="G47" t="s">
-        <v>80</v>
+        <v>49</v>
+      </c>
+      <c r="G47" t="n">
+        <v>3</v>
       </c>
       <c r="H47" t="s">
         <v>11</v>
@@ -1941,22 +1865,22 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C48" t="s">
-        <v>79</v>
+        <v>36</v>
       </c>
       <c r="D48" t="n">
-        <v>190</v>
+        <v>22407</v>
       </c>
       <c r="E48" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F48" t="s">
-        <v>67</v>
-      </c>
-      <c r="G48" t="s">
-        <v>81</v>
+        <v>49</v>
+      </c>
+      <c r="G48" t="n">
+        <v>64</v>
       </c>
       <c r="H48" t="s">
         <v>11</v>
@@ -1967,22 +1891,22 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="D49" t="n">
-        <v>190</v>
+        <v>22407</v>
       </c>
       <c r="E49" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="F49" t="s">
-        <v>68</v>
-      </c>
-      <c r="G49" t="s">
-        <v>82</v>
+        <v>49</v>
+      </c>
+      <c r="G49" t="n">
+        <v>53</v>
       </c>
       <c r="H49" t="s">
         <v>11</v>
@@ -1990,51 +1914,51 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="D50" t="n">
-        <v>190</v>
+        <v>6466</v>
       </c>
       <c r="E50" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F50" t="s">
-        <v>72</v>
-      </c>
-      <c r="G50" t="s">
-        <v>48</v>
+        <v>52</v>
+      </c>
+      <c r="G50" t="n">
+        <v>8</v>
       </c>
       <c r="H50" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" t="n">
+        <v>6466</v>
+      </c>
+      <c r="E51" t="s">
+        <v>51</v>
+      </c>
+      <c r="F51" t="s">
+        <v>52</v>
+      </c>
+      <c r="G51" t="n">
         <v>2</v>
-      </c>
-      <c r="B51" t="s">
-        <v>30</v>
-      </c>
-      <c r="C51" t="s">
-        <v>79</v>
-      </c>
-      <c r="D51" t="n">
-        <v>190</v>
-      </c>
-      <c r="E51" t="s">
-        <v>66</v>
-      </c>
-      <c r="F51" t="s">
-        <v>75</v>
-      </c>
-      <c r="G51" t="s">
-        <v>83</v>
       </c>
       <c r="H51" t="s">
         <v>11</v>
@@ -2042,25 +1966,25 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="C52" t="s">
-        <v>84</v>
+        <v>55</v>
       </c>
       <c r="D52" t="n">
-        <v>190</v>
+        <v>6466</v>
       </c>
       <c r="E52" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F52" t="s">
-        <v>69</v>
-      </c>
-      <c r="G52" t="s">
-        <v>39</v>
+        <v>52</v>
+      </c>
+      <c r="G52" t="n">
+        <v>13</v>
       </c>
       <c r="H52" t="s">
         <v>11</v>
@@ -2068,25 +1992,25 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C53" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="D53" t="n">
-        <v>190</v>
+        <v>6466</v>
       </c>
       <c r="E53" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F53" t="s">
-        <v>67</v>
-      </c>
-      <c r="G53" t="s">
-        <v>70</v>
+        <v>52</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8</v>
       </c>
       <c r="H53" t="s">
         <v>11</v>
@@ -2094,25 +2018,25 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C54" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="D54" t="n">
-        <v>190</v>
+        <v>6466</v>
       </c>
       <c r="E54" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F54" t="s">
-        <v>68</v>
-      </c>
-      <c r="G54" t="s">
-        <v>26</v>
+        <v>52</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4</v>
       </c>
       <c r="H54" t="s">
         <v>11</v>
@@ -2120,51 +2044,51 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C55" t="s">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="D55" t="n">
-        <v>190</v>
+        <v>6466</v>
       </c>
       <c r="E55" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F55" t="s">
-        <v>72</v>
-      </c>
-      <c r="G55" t="s">
-        <v>26</v>
+        <v>52</v>
+      </c>
+      <c r="G55" t="n">
+        <v>30</v>
       </c>
       <c r="H55" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C56" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="D56" t="n">
-        <v>190</v>
+        <v>6466</v>
       </c>
       <c r="E56" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F56" t="s">
-        <v>75</v>
-      </c>
-      <c r="G56" t="s">
-        <v>41</v>
+        <v>52</v>
+      </c>
+      <c r="G56" t="n">
+        <v>15</v>
       </c>
       <c r="H56" t="s">
         <v>11</v>
@@ -2172,25 +2096,25 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C57" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="D57" t="n">
-        <v>190</v>
+        <v>6466</v>
       </c>
       <c r="E57" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F57" t="s">
-        <v>69</v>
-      </c>
-      <c r="G57" t="s">
-        <v>26</v>
+        <v>52</v>
+      </c>
+      <c r="G57" t="n">
+        <v>10</v>
       </c>
       <c r="H57" t="s">
         <v>11</v>
@@ -2198,51 +2122,51 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C58" t="s">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="D58" t="n">
-        <v>190</v>
+        <v>6466</v>
       </c>
       <c r="E58" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F58" t="s">
-        <v>72</v>
-      </c>
-      <c r="G58" t="s">
-        <v>26</v>
+        <v>52</v>
+      </c>
+      <c r="G58" t="n">
+        <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="C59" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="D59" t="n">
-        <v>190</v>
+        <v>6466</v>
       </c>
       <c r="E59" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F59" t="s">
-        <v>69</v>
-      </c>
-      <c r="G59" t="s">
-        <v>26</v>
+        <v>52</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1428</v>
       </c>
       <c r="H59" t="s">
         <v>11</v>
@@ -2250,885 +2174,27 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="C60" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="D60" t="n">
-        <v>190</v>
+        <v>6466</v>
       </c>
       <c r="E60" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>67</v>
-      </c>
-      <c r="G60" t="s">
-        <v>26</v>
+        <v>52</v>
+      </c>
+      <c r="G60" t="n">
+        <v>48</v>
       </c>
       <c r="H60" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2</v>
-      </c>
-      <c r="B61" t="s">
-        <v>47</v>
-      </c>
-      <c r="C61" t="s">
-        <v>88</v>
-      </c>
-      <c r="D61" t="n">
-        <v>190</v>
-      </c>
-      <c r="E61" t="s">
-        <v>66</v>
-      </c>
-      <c r="F61" t="s">
-        <v>68</v>
-      </c>
-      <c r="G61" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>2</v>
-      </c>
-      <c r="B62" t="s">
-        <v>47</v>
-      </c>
-      <c r="C62" t="s">
-        <v>88</v>
-      </c>
-      <c r="D62" t="n">
-        <v>190</v>
-      </c>
-      <c r="E62" t="s">
-        <v>66</v>
-      </c>
-      <c r="F62" t="s">
-        <v>72</v>
-      </c>
-      <c r="G62" t="s">
-        <v>39</v>
-      </c>
-      <c r="H62" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>47</v>
-      </c>
-      <c r="C63" t="s">
-        <v>88</v>
-      </c>
-      <c r="D63" t="n">
-        <v>190</v>
-      </c>
-      <c r="E63" t="s">
-        <v>66</v>
-      </c>
-      <c r="F63" t="s">
-        <v>75</v>
-      </c>
-      <c r="G63" t="s">
-        <v>26</v>
-      </c>
-      <c r="H63" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>3</v>
-      </c>
-      <c r="B64" t="s">
-        <v>14</v>
-      </c>
-      <c r="C64" t="s">
-        <v>65</v>
-      </c>
-      <c r="D64" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E64" t="s">
-        <v>89</v>
-      </c>
-      <c r="F64" t="s">
-        <v>67</v>
-      </c>
-      <c r="G64" t="s">
-        <v>26</v>
-      </c>
-      <c r="H64" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>3</v>
-      </c>
-      <c r="B65" t="s">
-        <v>14</v>
-      </c>
-      <c r="C65" t="s">
-        <v>65</v>
-      </c>
-      <c r="D65" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E65" t="s">
-        <v>89</v>
-      </c>
-      <c r="F65" t="s">
-        <v>68</v>
-      </c>
-      <c r="G65" t="s">
-        <v>26</v>
-      </c>
-      <c r="H65" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>3</v>
-      </c>
-      <c r="B66" t="s">
-        <v>21</v>
-      </c>
-      <c r="C66" t="s">
-        <v>22</v>
-      </c>
-      <c r="D66" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E66" t="s">
-        <v>89</v>
-      </c>
-      <c r="F66" t="s">
-        <v>69</v>
-      </c>
-      <c r="G66" t="s">
-        <v>70</v>
-      </c>
-      <c r="H66" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>3</v>
-      </c>
-      <c r="B67" t="s">
-        <v>21</v>
-      </c>
-      <c r="C67" t="s">
-        <v>22</v>
-      </c>
-      <c r="D67" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E67" t="s">
-        <v>89</v>
-      </c>
-      <c r="F67" t="s">
-        <v>67</v>
-      </c>
-      <c r="G67" t="s">
-        <v>71</v>
-      </c>
-      <c r="H67" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>3</v>
-      </c>
-      <c r="B68" t="s">
-        <v>21</v>
-      </c>
-      <c r="C68" t="s">
-        <v>22</v>
-      </c>
-      <c r="D68" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E68" t="s">
-        <v>89</v>
-      </c>
-      <c r="F68" t="s">
-        <v>68</v>
-      </c>
-      <c r="G68" t="s">
-        <v>50</v>
-      </c>
-      <c r="H68" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>3</v>
-      </c>
-      <c r="B69" t="s">
-        <v>21</v>
-      </c>
-      <c r="C69" t="s">
-        <v>22</v>
-      </c>
-      <c r="D69" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E69" t="s">
-        <v>89</v>
-      </c>
-      <c r="F69" t="s">
-        <v>72</v>
-      </c>
-      <c r="G69" t="s">
-        <v>73</v>
-      </c>
-      <c r="H69" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>3</v>
-      </c>
-      <c r="B70" t="s">
-        <v>21</v>
-      </c>
-      <c r="C70" t="s">
-        <v>22</v>
-      </c>
-      <c r="D70" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E70" t="s">
-        <v>89</v>
-      </c>
-      <c r="F70" t="s">
-        <v>75</v>
-      </c>
-      <c r="G70" t="s">
-        <v>24</v>
-      </c>
-      <c r="H70" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>3</v>
-      </c>
-      <c r="B71" t="s">
-        <v>76</v>
-      </c>
-      <c r="C71" t="s">
-        <v>77</v>
-      </c>
-      <c r="D71" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E71" t="s">
-        <v>89</v>
-      </c>
-      <c r="F71" t="s">
-        <v>69</v>
-      </c>
-      <c r="G71" t="s">
-        <v>37</v>
-      </c>
-      <c r="H71" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>3</v>
-      </c>
-      <c r="B72" t="s">
-        <v>76</v>
-      </c>
-      <c r="C72" t="s">
-        <v>77</v>
-      </c>
-      <c r="D72" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E72" t="s">
-        <v>89</v>
-      </c>
-      <c r="F72" t="s">
-        <v>67</v>
-      </c>
-      <c r="G72" t="s">
-        <v>39</v>
-      </c>
-      <c r="H72" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>3</v>
-      </c>
-      <c r="B73" t="s">
-        <v>76</v>
-      </c>
-      <c r="C73" t="s">
-        <v>77</v>
-      </c>
-      <c r="D73" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E73" t="s">
-        <v>89</v>
-      </c>
-      <c r="F73" t="s">
-        <v>68</v>
-      </c>
-      <c r="G73" t="s">
-        <v>41</v>
-      </c>
-      <c r="H73" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>3</v>
-      </c>
-      <c r="B74" t="s">
-        <v>27</v>
-      </c>
-      <c r="C74" t="s">
-        <v>78</v>
-      </c>
-      <c r="D74" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E74" t="s">
-        <v>89</v>
-      </c>
-      <c r="F74" t="s">
-        <v>68</v>
-      </c>
-      <c r="G74" t="s">
-        <v>26</v>
-      </c>
-      <c r="H74" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>3</v>
-      </c>
-      <c r="B75" t="s">
-        <v>27</v>
-      </c>
-      <c r="C75" t="s">
-        <v>78</v>
-      </c>
-      <c r="D75" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E75" t="s">
-        <v>89</v>
-      </c>
-      <c r="F75" t="s">
-        <v>72</v>
-      </c>
-      <c r="G75" t="s">
-        <v>26</v>
-      </c>
-      <c r="H75" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>3</v>
-      </c>
-      <c r="B76" t="s">
-        <v>27</v>
-      </c>
-      <c r="C76" t="s">
-        <v>78</v>
-      </c>
-      <c r="D76" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E76" t="s">
-        <v>89</v>
-      </c>
-      <c r="F76" t="s">
-        <v>75</v>
-      </c>
-      <c r="G76" t="s">
-        <v>39</v>
-      </c>
-      <c r="H76" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>3</v>
-      </c>
-      <c r="B77" t="s">
-        <v>30</v>
-      </c>
-      <c r="C77" t="s">
-        <v>79</v>
-      </c>
-      <c r="D77" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E77" t="s">
-        <v>89</v>
-      </c>
-      <c r="F77" t="s">
-        <v>69</v>
-      </c>
-      <c r="G77" t="s">
-        <v>80</v>
-      </c>
-      <c r="H77" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>3</v>
-      </c>
-      <c r="B78" t="s">
-        <v>30</v>
-      </c>
-      <c r="C78" t="s">
-        <v>79</v>
-      </c>
-      <c r="D78" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E78" t="s">
-        <v>89</v>
-      </c>
-      <c r="F78" t="s">
-        <v>67</v>
-      </c>
-      <c r="G78" t="s">
-        <v>81</v>
-      </c>
-      <c r="H78" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>3</v>
-      </c>
-      <c r="B79" t="s">
-        <v>30</v>
-      </c>
-      <c r="C79" t="s">
-        <v>79</v>
-      </c>
-      <c r="D79" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E79" t="s">
-        <v>89</v>
-      </c>
-      <c r="F79" t="s">
-        <v>68</v>
-      </c>
-      <c r="G79" t="s">
-        <v>82</v>
-      </c>
-      <c r="H79" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>3</v>
-      </c>
-      <c r="B80" t="s">
-        <v>30</v>
-      </c>
-      <c r="C80" t="s">
-        <v>79</v>
-      </c>
-      <c r="D80" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E80" t="s">
-        <v>89</v>
-      </c>
-      <c r="F80" t="s">
-        <v>72</v>
-      </c>
-      <c r="G80" t="s">
-        <v>48</v>
-      </c>
-      <c r="H80" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>3</v>
-      </c>
-      <c r="B81" t="s">
-        <v>30</v>
-      </c>
-      <c r="C81" t="s">
-        <v>79</v>
-      </c>
-      <c r="D81" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E81" t="s">
-        <v>89</v>
-      </c>
-      <c r="F81" t="s">
-        <v>75</v>
-      </c>
-      <c r="G81" t="s">
-        <v>83</v>
-      </c>
-      <c r="H81" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>3</v>
-      </c>
-      <c r="B82" t="s">
-        <v>32</v>
-      </c>
-      <c r="C82" t="s">
-        <v>84</v>
-      </c>
-      <c r="D82" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E82" t="s">
-        <v>89</v>
-      </c>
-      <c r="F82" t="s">
-        <v>69</v>
-      </c>
-      <c r="G82" t="s">
-        <v>39</v>
-      </c>
-      <c r="H82" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>3</v>
-      </c>
-      <c r="B83" t="s">
-        <v>32</v>
-      </c>
-      <c r="C83" t="s">
-        <v>84</v>
-      </c>
-      <c r="D83" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E83" t="s">
-        <v>89</v>
-      </c>
-      <c r="F83" t="s">
-        <v>67</v>
-      </c>
-      <c r="G83" t="s">
-        <v>70</v>
-      </c>
-      <c r="H83" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>3</v>
-      </c>
-      <c r="B84" t="s">
-        <v>32</v>
-      </c>
-      <c r="C84" t="s">
-        <v>84</v>
-      </c>
-      <c r="D84" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E84" t="s">
-        <v>89</v>
-      </c>
-      <c r="F84" t="s">
-        <v>68</v>
-      </c>
-      <c r="G84" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>3</v>
-      </c>
-      <c r="B85" t="s">
-        <v>32</v>
-      </c>
-      <c r="C85" t="s">
-        <v>84</v>
-      </c>
-      <c r="D85" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E85" t="s">
-        <v>89</v>
-      </c>
-      <c r="F85" t="s">
-        <v>72</v>
-      </c>
-      <c r="G85" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>3</v>
-      </c>
-      <c r="B86" t="s">
-        <v>32</v>
-      </c>
-      <c r="C86" t="s">
-        <v>84</v>
-      </c>
-      <c r="D86" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E86" t="s">
-        <v>89</v>
-      </c>
-      <c r="F86" t="s">
-        <v>75</v>
-      </c>
-      <c r="G86" t="s">
-        <v>41</v>
-      </c>
-      <c r="H86" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>3</v>
-      </c>
-      <c r="B87" t="s">
-        <v>35</v>
-      </c>
-      <c r="C87" t="s">
-        <v>85</v>
-      </c>
-      <c r="D87" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E87" t="s">
-        <v>89</v>
-      </c>
-      <c r="F87" t="s">
-        <v>69</v>
-      </c>
-      <c r="G87" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>3</v>
-      </c>
-      <c r="B88" t="s">
-        <v>35</v>
-      </c>
-      <c r="C88" t="s">
-        <v>85</v>
-      </c>
-      <c r="D88" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E88" t="s">
-        <v>89</v>
-      </c>
-      <c r="F88" t="s">
-        <v>72</v>
-      </c>
-      <c r="G88" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>3</v>
-      </c>
-      <c r="B89" t="s">
-        <v>86</v>
-      </c>
-      <c r="C89" t="s">
-        <v>87</v>
-      </c>
-      <c r="D89" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E89" t="s">
-        <v>89</v>
-      </c>
-      <c r="F89" t="s">
-        <v>69</v>
-      </c>
-      <c r="G89" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>3</v>
-      </c>
-      <c r="B90" t="s">
-        <v>86</v>
-      </c>
-      <c r="C90" t="s">
-        <v>87</v>
-      </c>
-      <c r="D90" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E90" t="s">
-        <v>89</v>
-      </c>
-      <c r="F90" t="s">
-        <v>67</v>
-      </c>
-      <c r="G90" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>3</v>
-      </c>
-      <c r="B91" t="s">
-        <v>47</v>
-      </c>
-      <c r="C91" t="s">
-        <v>88</v>
-      </c>
-      <c r="D91" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E91" t="s">
-        <v>89</v>
-      </c>
-      <c r="F91" t="s">
-        <v>68</v>
-      </c>
-      <c r="G91" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
-        <v>3</v>
-      </c>
-      <c r="B92" t="s">
-        <v>47</v>
-      </c>
-      <c r="C92" t="s">
-        <v>88</v>
-      </c>
-      <c r="D92" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E92" t="s">
-        <v>89</v>
-      </c>
-      <c r="F92" t="s">
-        <v>72</v>
-      </c>
-      <c r="G92" t="s">
-        <v>39</v>
-      </c>
-      <c r="H92" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
-        <v>3</v>
-      </c>
-      <c r="B93" t="s">
-        <v>47</v>
-      </c>
-      <c r="C93" t="s">
-        <v>88</v>
-      </c>
-      <c r="D93" t="n">
-        <v>2808</v>
-      </c>
-      <c r="E93" t="s">
-        <v>89</v>
-      </c>
-      <c r="F93" t="s">
-        <v>75</v>
-      </c>
-      <c r="G93" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" t="s">
         <v>11</v>
       </c>
     </row>

--- a/FaunalListoR_data.xlsx
+++ b/FaunalListoR_data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">id_faunalstudy</t>
   </si>
@@ -66,6 +66,12 @@
     <t xml:space="preserve">faunal study combines couches 4 et 5</t>
   </si>
   <si>
+    <t xml:space="preserve">Rhodes II</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
     <t xml:space="preserve">taxon_unified</t>
   </si>
   <si>
@@ -199,6 +205,30 @@
   </si>
   <si>
     <t xml:space="preserve">Rupicapra rupicapra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c.2 - F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capra cf. pyrenaica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rupicapra cf. pyrenaica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c.1 - F6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c.1 - F7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F7</t>
   </si>
 </sst>
 </file>
@@ -627,6 +657,32 @@
         <v>16</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4778</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2015</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -643,22 +699,22 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H1" t="s">
         <v>6</v>
@@ -669,19 +725,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
         <v>19490</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G2" t="n">
         <v>18</v>
@@ -695,19 +751,19 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="n">
         <v>19490</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -721,19 +777,19 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
         <v>19490</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
         <v>33</v>
@@ -747,19 +803,19 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
         <v>19490</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
         <v>18</v>
@@ -773,19 +829,19 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" t="n">
         <v>19490</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
         <v>196</v>
@@ -799,19 +855,19 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" t="n">
         <v>19490</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G7" t="n">
         <v>13</v>
@@ -825,19 +881,19 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
         <v>19490</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G8" t="n">
         <v>3</v>
@@ -851,19 +907,19 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
         <v>19490</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
@@ -877,19 +933,19 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" t="n">
         <v>19490</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
@@ -903,19 +959,19 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" t="n">
         <v>19490</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G11" t="n">
         <v>8</v>
@@ -929,19 +985,19 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D12" t="n">
         <v>19490</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
         <v>107</v>
@@ -955,19 +1011,19 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D13" t="n">
         <v>19490</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G13" t="n">
         <v>18</v>
@@ -981,19 +1037,19 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
         <v>19490</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G14" t="n">
         <v>9</v>
@@ -1007,19 +1063,19 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D15" t="n">
         <v>19490</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G15" t="n">
         <v>26</v>
@@ -1033,19 +1089,19 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D16" t="n">
         <v>19490</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
@@ -1059,19 +1115,19 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D17" t="n">
         <v>19491</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
         <v>90</v>
@@ -1085,19 +1141,19 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
         <v>19491</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F18" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
         <v>3</v>
@@ -1111,19 +1167,19 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
         <v>19491</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G19" t="n">
         <v>55</v>
@@ -1137,19 +1193,19 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D20" t="n">
         <v>19491</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F20" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
         <v>37</v>
@@ -1163,19 +1219,19 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D21" t="n">
         <v>19491</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F21" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
         <v>664</v>
@@ -1189,19 +1245,19 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D22" t="n">
         <v>19491</v>
       </c>
       <c r="E22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
         <v>57</v>
@@ -1215,19 +1271,19 @@
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D23" t="n">
         <v>19491</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F23" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G23" t="n">
         <v>1</v>
@@ -1241,19 +1297,19 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C24" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D24" t="n">
         <v>19491</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G24" t="n">
         <v>4</v>
@@ -1267,19 +1323,19 @@
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D25" t="n">
         <v>19491</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G25" t="n">
         <v>50</v>
@@ -1293,19 +1349,19 @@
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D26" t="n">
         <v>19491</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F26" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G26" t="n">
         <v>3</v>
@@ -1319,19 +1375,19 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D27" t="n">
         <v>19491</v>
       </c>
       <c r="E27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F27" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G27" t="n">
         <v>47</v>
@@ -1345,19 +1401,19 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D28" t="n">
         <v>19491</v>
       </c>
       <c r="E28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G28" t="n">
         <v>171</v>
@@ -1371,19 +1427,19 @@
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C29" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D29" t="n">
         <v>19491</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G29" t="n">
         <v>72</v>
@@ -1397,19 +1453,19 @@
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D30" t="n">
         <v>19491</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -1423,19 +1479,19 @@
         <v>1</v>
       </c>
       <c r="B31" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D31" t="n">
         <v>19491</v>
       </c>
       <c r="E31" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F31" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G31" t="n">
         <v>211</v>
@@ -1449,19 +1505,19 @@
         <v>1</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D32" t="n">
         <v>19491</v>
       </c>
       <c r="E32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G32" t="n">
         <v>38</v>
@@ -1475,19 +1531,19 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D33" t="n">
         <v>22405</v>
       </c>
       <c r="E33" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F33" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G33" t="n">
         <v>3</v>
@@ -1501,19 +1557,19 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D34" t="n">
         <v>22405</v>
       </c>
       <c r="E34" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F34" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G34" t="n">
         <v>17</v>
@@ -1527,19 +1583,19 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D35" t="n">
         <v>22405</v>
       </c>
       <c r="E35" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F35" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G35" t="n">
         <v>34</v>
@@ -1553,19 +1609,19 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D36" t="n">
         <v>22405</v>
       </c>
       <c r="E36" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F36" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G36" t="n">
         <v>11</v>
@@ -1579,19 +1635,19 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C37" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D37" t="n">
         <v>22405</v>
       </c>
       <c r="E37" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F37" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G37" t="n">
         <v>5</v>
@@ -1605,19 +1661,19 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D38" t="n">
         <v>22405</v>
       </c>
       <c r="E38" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F38" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G38" t="n">
         <v>6596</v>
@@ -1631,19 +1687,19 @@
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D39" t="n">
         <v>22405</v>
       </c>
       <c r="E39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F39" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G39" t="n">
         <v>115</v>
@@ -1657,19 +1713,19 @@
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D40" t="n">
         <v>22405</v>
       </c>
       <c r="E40" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F40" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G40" t="n">
         <v>23</v>
@@ -1683,19 +1739,19 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C41" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D41" t="n">
         <v>22406</v>
       </c>
       <c r="E41" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F41" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G41" t="n">
         <v>7</v>
@@ -1709,19 +1765,19 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D42" t="n">
         <v>22406</v>
       </c>
       <c r="E42" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G42" t="n">
         <v>5</v>
@@ -1735,19 +1791,19 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D43" t="n">
         <v>22406</v>
       </c>
       <c r="E43" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F43" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G43" t="n">
         <v>1</v>
@@ -1761,19 +1817,19 @@
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C44" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D44" t="n">
         <v>22406</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F44" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G44" t="n">
         <v>230</v>
@@ -1787,19 +1843,19 @@
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C45" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D45" t="n">
         <v>22406</v>
       </c>
       <c r="E45" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F45" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G45" t="n">
         <v>15</v>
@@ -1813,19 +1869,19 @@
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C46" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D46" t="n">
         <v>22407</v>
       </c>
       <c r="E46" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F46" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G46" t="n">
         <v>3</v>
@@ -1839,19 +1895,19 @@
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C47" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D47" t="n">
         <v>22407</v>
       </c>
       <c r="E47" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F47" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G47" t="n">
         <v>3</v>
@@ -1865,19 +1921,19 @@
         <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C48" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D48" t="n">
         <v>22407</v>
       </c>
       <c r="E48" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F48" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G48" t="n">
         <v>64</v>
@@ -1891,19 +1947,19 @@
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C49" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D49" t="n">
         <v>22407</v>
       </c>
       <c r="E49" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F49" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G49" t="n">
         <v>53</v>
@@ -1917,19 +1973,19 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D50" t="n">
         <v>6466</v>
       </c>
       <c r="E50" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F50" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G50" t="n">
         <v>8</v>
@@ -1943,19 +1999,19 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D51" t="n">
         <v>6466</v>
       </c>
       <c r="E51" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F51" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
@@ -1969,19 +2025,19 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C52" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D52" t="n">
         <v>6466</v>
       </c>
       <c r="E52" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F52" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G52" t="n">
         <v>13</v>
@@ -1995,19 +2051,19 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D53" t="n">
         <v>6466</v>
       </c>
       <c r="E53" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F53" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G53" t="n">
         <v>8</v>
@@ -2021,19 +2077,19 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D54" t="n">
         <v>6466</v>
       </c>
       <c r="E54" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F54" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G54" t="n">
         <v>4</v>
@@ -2047,19 +2103,19 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C55" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D55" t="n">
         <v>6466</v>
       </c>
       <c r="E55" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F55" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G55" t="n">
         <v>30</v>
@@ -2073,19 +2129,19 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D56" t="n">
         <v>6466</v>
       </c>
       <c r="E56" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F56" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G56" t="n">
         <v>15</v>
@@ -2099,19 +2155,19 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C57" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D57" t="n">
         <v>6466</v>
       </c>
       <c r="E57" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F57" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G57" t="n">
         <v>10</v>
@@ -2125,19 +2181,19 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C58" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D58" t="n">
         <v>6466</v>
       </c>
       <c r="E58" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F58" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G58" t="n">
         <v>1</v>
@@ -2151,19 +2207,19 @@
         <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D59" t="n">
         <v>6466</v>
       </c>
       <c r="E59" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F59" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G59" t="n">
         <v>1428</v>
@@ -2177,24 +2233,778 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D60" t="n">
         <v>6466</v>
       </c>
       <c r="E60" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F60" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G60" t="n">
         <v>48</v>
       </c>
       <c r="H60" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" t="s">
+        <v>25</v>
+      </c>
+      <c r="C61" t="s">
+        <v>26</v>
+      </c>
+      <c r="D61" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E61" t="s">
+        <v>64</v>
+      </c>
+      <c r="F61" t="s">
+        <v>65</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B62" t="s">
+        <v>28</v>
+      </c>
+      <c r="C62" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E62" t="s">
+        <v>64</v>
+      </c>
+      <c r="F62" t="s">
+        <v>65</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>4</v>
+      </c>
+      <c r="B63" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" t="s">
+        <v>66</v>
+      </c>
+      <c r="D63" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E63" t="s">
+        <v>64</v>
+      </c>
+      <c r="F63" t="s">
+        <v>65</v>
+      </c>
+      <c r="G63" t="n">
+        <v>228</v>
+      </c>
+      <c r="H63" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>4</v>
+      </c>
+      <c r="B64" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E64" t="s">
+        <v>64</v>
+      </c>
+      <c r="F64" t="s">
+        <v>65</v>
+      </c>
+      <c r="G64" t="n">
+        <v>56</v>
+      </c>
+      <c r="H64" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" t="s">
+        <v>30</v>
+      </c>
+      <c r="C65" t="s">
+        <v>30</v>
+      </c>
+      <c r="D65" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E65" t="s">
+        <v>64</v>
+      </c>
+      <c r="F65" t="s">
+        <v>65</v>
+      </c>
+      <c r="G65" t="n">
+        <v>3</v>
+      </c>
+      <c r="H65" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>4</v>
+      </c>
+      <c r="B66" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" t="s">
+        <v>31</v>
+      </c>
+      <c r="D66" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E66" t="s">
+        <v>64</v>
+      </c>
+      <c r="F66" t="s">
+        <v>65</v>
+      </c>
+      <c r="G66" t="n">
+        <v>134</v>
+      </c>
+      <c r="H66" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>4</v>
+      </c>
+      <c r="B67" t="s">
+        <v>37</v>
+      </c>
+      <c r="C67" t="s">
+        <v>37</v>
+      </c>
+      <c r="D67" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E67" t="s">
+        <v>64</v>
+      </c>
+      <c r="F67" t="s">
+        <v>65</v>
+      </c>
+      <c r="G67" t="n">
+        <v>1</v>
+      </c>
+      <c r="H67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>38</v>
+      </c>
+      <c r="C68" t="s">
+        <v>38</v>
+      </c>
+      <c r="D68" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E68" t="s">
+        <v>64</v>
+      </c>
+      <c r="F68" t="s">
+        <v>65</v>
+      </c>
+      <c r="G68" t="n">
+        <v>23</v>
+      </c>
+      <c r="H68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69" t="s">
+        <v>67</v>
+      </c>
+      <c r="D69" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E69" t="s">
+        <v>64</v>
+      </c>
+      <c r="F69" t="s">
+        <v>65</v>
+      </c>
+      <c r="G69" t="n">
+        <v>17</v>
+      </c>
+      <c r="H69" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" t="s">
+        <v>41</v>
+      </c>
+      <c r="D70" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E70" t="s">
+        <v>64</v>
+      </c>
+      <c r="F70" t="s">
+        <v>65</v>
+      </c>
+      <c r="G70" t="n">
+        <v>30</v>
+      </c>
+      <c r="H70" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>4</v>
+      </c>
+      <c r="B71" t="s">
+        <v>42</v>
+      </c>
+      <c r="C71" t="s">
+        <v>42</v>
+      </c>
+      <c r="D71" t="n">
+        <v>22914</v>
+      </c>
+      <c r="E71" t="s">
+        <v>64</v>
+      </c>
+      <c r="F71" t="s">
+        <v>65</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>4</v>
+      </c>
+      <c r="B72" t="s">
+        <v>28</v>
+      </c>
+      <c r="C72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D72" t="n">
+        <v>22915</v>
+      </c>
+      <c r="E72" t="s">
+        <v>68</v>
+      </c>
+      <c r="F72" t="s">
+        <v>69</v>
+      </c>
+      <c r="G72" t="n">
+        <v>3</v>
+      </c>
+      <c r="H72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>4</v>
+      </c>
+      <c r="B73" t="s">
+        <v>56</v>
+      </c>
+      <c r="C73" t="s">
+        <v>66</v>
+      </c>
+      <c r="D73" t="n">
+        <v>22915</v>
+      </c>
+      <c r="E73" t="s">
+        <v>68</v>
+      </c>
+      <c r="F73" t="s">
+        <v>69</v>
+      </c>
+      <c r="G73" t="n">
+        <v>27</v>
+      </c>
+      <c r="H73" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" t="n">
+        <v>22915</v>
+      </c>
+      <c r="E74" t="s">
+        <v>68</v>
+      </c>
+      <c r="F74" t="s">
+        <v>69</v>
+      </c>
+      <c r="G74" t="n">
+        <v>15</v>
+      </c>
+      <c r="H74" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>4</v>
+      </c>
+      <c r="B75" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" t="s">
+        <v>31</v>
+      </c>
+      <c r="D75" t="n">
+        <v>22915</v>
+      </c>
+      <c r="E75" t="s">
+        <v>68</v>
+      </c>
+      <c r="F75" t="s">
+        <v>69</v>
+      </c>
+      <c r="G75" t="n">
+        <v>92</v>
+      </c>
+      <c r="H75" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>37</v>
+      </c>
+      <c r="C76" t="s">
+        <v>37</v>
+      </c>
+      <c r="D76" t="n">
+        <v>22915</v>
+      </c>
+      <c r="E76" t="s">
+        <v>68</v>
+      </c>
+      <c r="F76" t="s">
+        <v>69</v>
+      </c>
+      <c r="G76" t="n">
+        <v>1</v>
+      </c>
+      <c r="H76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>4</v>
+      </c>
+      <c r="B77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C77" t="s">
+        <v>38</v>
+      </c>
+      <c r="D77" t="n">
+        <v>22915</v>
+      </c>
+      <c r="E77" t="s">
+        <v>68</v>
+      </c>
+      <c r="F77" t="s">
+        <v>69</v>
+      </c>
+      <c r="G77" t="n">
+        <v>6</v>
+      </c>
+      <c r="H77" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>40</v>
+      </c>
+      <c r="C78" t="s">
+        <v>67</v>
+      </c>
+      <c r="D78" t="n">
+        <v>22915</v>
+      </c>
+      <c r="E78" t="s">
+        <v>68</v>
+      </c>
+      <c r="F78" t="s">
+        <v>69</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4</v>
+      </c>
+      <c r="H78" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>4</v>
+      </c>
+      <c r="B79" t="s">
+        <v>41</v>
+      </c>
+      <c r="C79" t="s">
+        <v>41</v>
+      </c>
+      <c r="D79" t="n">
+        <v>22915</v>
+      </c>
+      <c r="E79" t="s">
+        <v>68</v>
+      </c>
+      <c r="F79" t="s">
+        <v>69</v>
+      </c>
+      <c r="G79" t="n">
+        <v>28</v>
+      </c>
+      <c r="H79" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4</v>
+      </c>
+      <c r="B80" t="s">
+        <v>42</v>
+      </c>
+      <c r="C80" t="s">
+        <v>42</v>
+      </c>
+      <c r="D80" t="n">
+        <v>22915</v>
+      </c>
+      <c r="E80" t="s">
+        <v>68</v>
+      </c>
+      <c r="F80" t="s">
+        <v>69</v>
+      </c>
+      <c r="G80" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4</v>
+      </c>
+      <c r="B81" t="s">
+        <v>56</v>
+      </c>
+      <c r="C81" t="s">
+        <v>66</v>
+      </c>
+      <c r="D81" t="n">
+        <v>22916</v>
+      </c>
+      <c r="E81" t="s">
+        <v>70</v>
+      </c>
+      <c r="F81" t="s">
+        <v>71</v>
+      </c>
+      <c r="G81" t="n">
+        <v>48</v>
+      </c>
+      <c r="H81" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4</v>
+      </c>
+      <c r="B82" t="s">
+        <v>29</v>
+      </c>
+      <c r="C82" t="s">
+        <v>29</v>
+      </c>
+      <c r="D82" t="n">
+        <v>22916</v>
+      </c>
+      <c r="E82" t="s">
+        <v>70</v>
+      </c>
+      <c r="F82" t="s">
+        <v>71</v>
+      </c>
+      <c r="G82" t="n">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4</v>
+      </c>
+      <c r="B83" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" t="s">
+        <v>31</v>
+      </c>
+      <c r="D83" t="n">
+        <v>22916</v>
+      </c>
+      <c r="E83" t="s">
+        <v>70</v>
+      </c>
+      <c r="F83" t="s">
+        <v>71</v>
+      </c>
+      <c r="G83" t="n">
+        <v>278</v>
+      </c>
+      <c r="H83" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4</v>
+      </c>
+      <c r="B84" t="s">
+        <v>34</v>
+      </c>
+      <c r="C84" t="s">
+        <v>34</v>
+      </c>
+      <c r="D84" t="n">
+        <v>22916</v>
+      </c>
+      <c r="E84" t="s">
+        <v>70</v>
+      </c>
+      <c r="F84" t="s">
+        <v>71</v>
+      </c>
+      <c r="G84" t="n">
+        <v>1</v>
+      </c>
+      <c r="H84" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4</v>
+      </c>
+      <c r="B85" t="s">
+        <v>36</v>
+      </c>
+      <c r="C85" t="s">
+        <v>36</v>
+      </c>
+      <c r="D85" t="n">
+        <v>22916</v>
+      </c>
+      <c r="E85" t="s">
+        <v>70</v>
+      </c>
+      <c r="F85" t="s">
+        <v>71</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4</v>
+      </c>
+      <c r="B86" t="s">
+        <v>37</v>
+      </c>
+      <c r="C86" t="s">
+        <v>37</v>
+      </c>
+      <c r="D86" t="n">
+        <v>22916</v>
+      </c>
+      <c r="E86" t="s">
+        <v>70</v>
+      </c>
+      <c r="F86" t="s">
+        <v>71</v>
+      </c>
+      <c r="G86" t="n">
+        <v>4</v>
+      </c>
+      <c r="H86" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4</v>
+      </c>
+      <c r="B87" t="s">
+        <v>38</v>
+      </c>
+      <c r="C87" t="s">
+        <v>38</v>
+      </c>
+      <c r="D87" t="n">
+        <v>22916</v>
+      </c>
+      <c r="E87" t="s">
+        <v>70</v>
+      </c>
+      <c r="F87" t="s">
+        <v>71</v>
+      </c>
+      <c r="G87" t="n">
+        <v>5</v>
+      </c>
+      <c r="H87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4</v>
+      </c>
+      <c r="B88" t="s">
+        <v>41</v>
+      </c>
+      <c r="C88" t="s">
+        <v>41</v>
+      </c>
+      <c r="D88" t="n">
+        <v>22916</v>
+      </c>
+      <c r="E88" t="s">
+        <v>70</v>
+      </c>
+      <c r="F88" t="s">
+        <v>71</v>
+      </c>
+      <c r="G88" t="n">
+        <v>107</v>
+      </c>
+      <c r="H88" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>4</v>
+      </c>
+      <c r="B89" t="s">
+        <v>42</v>
+      </c>
+      <c r="C89" t="s">
+        <v>42</v>
+      </c>
+      <c r="D89" t="n">
+        <v>22916</v>
+      </c>
+      <c r="E89" t="s">
+        <v>70</v>
+      </c>
+      <c r="F89" t="s">
+        <v>71</v>
+      </c>
+      <c r="G89" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
         <v>11</v>
       </c>
     </row>
